--- a/report_agent/output/risk_assessment_form/risk_assessment_form_filled.xlsx
+++ b/report_agent/output/risk_assessment_form/risk_assessment_form_filled.xlsx
@@ -2641,7 +2641,7 @@
       </c>
       <c r="M21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">리포트에 이상이 있다</t>
+          <t xml:space="preserve">리포트가 이상하다</t>
         </is>
       </c>
       <c r="N21" t="inlineStr" s="0">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="O21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">조치 위치를 확인해야 한다</t>
+          <t xml:space="preserve">조치 위치 확인 필요</t>
         </is>
       </c>
       <c r="P21" t="inlineStr" s="3">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="M22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">게시판-조치테이블-담당자 배정 및 보고서 생성</t>
+          <t xml:space="preserve">게시판-조치테이블-담당자 배정 리포트 생성</t>
         </is>
       </c>
       <c r="N22" t="inlineStr" s="0">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="M24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">worker10 조치 완료</t>
+          <t xml:space="preserve">worker10 조치</t>
         </is>
       </c>
       <c r="N24" t="inlineStr" s="0">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="O24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">,</t>
         </is>
       </c>
       <c r="P24" t="inlineStr" s="3">

--- a/report_agent/output/risk_assessment_form/risk_assessment_form_filled.xlsx
+++ b/report_agent/output/risk_assessment_form/risk_assessment_form_filled.xlsx
@@ -300,7 +300,7 @@
       </c>
       <c r="B3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2026-08-07</t>
+          <t xml:space="preserve">2026-08-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="0">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="I9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">조치가 필요하다.</t>
+          <t xml:space="preserve">조치가 필요하다고 확인됐다.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr" s="0">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="I11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">조치가 필요하다.</t>
+          <t xml:space="preserve">조치가 필요하다고 확인됐다.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr" s="0">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="I14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">조치가 필요하다.</t>
+          <t xml:space="preserve">조치가 필요하다고 확인됐다.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr" s="0">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">조치가 필요하다.</t>
+          <t xml:space="preserve">조치가 필요하다고 확인됐다.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr" s="0">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="M21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">리포트가 이상하다</t>
+          <t xml:space="preserve">리포트에 이상이 있다</t>
         </is>
       </c>
       <c r="N21" t="inlineStr" s="0">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="O21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">조치 위치 확인 필요</t>
+          <t xml:space="preserve">살려주세요</t>
         </is>
       </c>
       <c r="P21" t="inlineStr" s="3">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="M22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">게시판-조치테이블-담당자 배정 리포트 생성</t>
+          <t xml:space="preserve">게시판-조치테이블-담당자 배정 및 리포트 생성</t>
         </is>
       </c>
       <c r="N22" t="inlineStr" s="0">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="M23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">조치 이름이 Action_name에 들어가는지 확인</t>
+          <t xml:space="preserve">조치명(Action_name) 적합성 확인</t>
         </is>
       </c>
       <c r="N23" t="inlineStr" s="0">

--- a/report_agent/output/risk_assessment_form/risk_assessment_form_filled.xlsx
+++ b/report_agent/output/risk_assessment_form/risk_assessment_form_filled.xlsx
@@ -124,107 +124,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1143000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="1143000" cy="762000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1143000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="1143000" cy="762000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1143000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="1143000" cy="762000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -547,7 +447,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">본 점검에 대한 조치가 필요하다.</t>
+          <t xml:space="preserve">조치가 필요하다.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -801,7 +701,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">본 점검에 대한 조치가 필요하다.</t>
+          <t xml:space="preserve">조치가 필요하다.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1182,7 +1082,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">본 점검에 대한 조치가 필요하다.</t>
+          <t xml:space="preserve">조치가 필요하다.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1964,7 +1864,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">소화기 배치 상태를 점검했다</t>
+          <t xml:space="preserve">소화기 배치 상태 점검을 실시했다</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2081,7 +1981,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">http://127.0.0.1:8000/static/uploads/action_history_44_20260805161205525013_78ff6b6a.png</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2285,7 +2185,7 @@
     <row r="23" spans="1:25" ht="48" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ㄴㄴ</t>
+          <t xml:space="preserve">화재 감지</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2295,7 +2195,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타</t>
+          <t xml:space="preserve">소방안전</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2345,7 +2245,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">조치명(Action_name) 입력 여부 확인</t>
+          <t xml:space="preserve">작업자10 조치를 실시했다</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2355,12 +2255,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">집</t>
+          <t xml:space="preserve">,</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05 16:08:25</t>
+          <t xml:space="preserve">2026-08-03 10:18:24</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2370,7 +2270,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업자23</t>
+          <t xml:space="preserve">작업자10</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2390,7 +2290,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://127.0.0.1:8000/static/uploads/action_history_42_20260805160825009402_7d15c7db.png</t>
+          <t xml:space="preserve">http://127.0.0.1:8000/static/uploads/action_history_21_20260803101823659726_cdfaccd8.png</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -2405,7 +2305,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t xml:space="preserve">게시판</t>
+          <t xml:space="preserve">직접추가</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2372,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker10 조치를 실시했다</t>
+          <t xml:space="preserve">A동 복도 소화기 배치 재점검을 요청했다</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2482,12 +2382,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">,</t>
+          <t xml:space="preserve">A동 복도</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-03 10:18:24</t>
+          <t xml:space="preserve">2026-07-29 06:43:54</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2497,7 +2397,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업자10</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2517,7 +2417,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://127.0.0.1:8000/static/uploads/action_history_21_20260803101823659726_cdfaccd8.png</t>
+          <t xml:space="preserve">http://127.0.0.1:8000/static/uploads/board_1785201730.jpg</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -2527,137 +2427,10 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t xml:space="preserve">판교관리자</t>
+          <t xml:space="preserve">현수</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">직접추가</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" spans="1:25" ht="48" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화재 감지</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소방안전</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A동 복도 소화기 배치 재점검을 요청했다</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A동 복도</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-29 06:43:54</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">http://127.0.0.1:8000/static/uploads/board_1785201730.jpg</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">현수</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
         <is>
           <t xml:space="preserve">게시판</t>
         </is>
